--- a/Книга1.xlsx
+++ b/Книга1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/domino_nil/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73381CB4-16B8-E54D-AC85-DF48E208D67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8299270B-61BE-8240-B113-5555494A2AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{673FFA90-7DB2-BF4A-8567-FED6D317E3AE}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="63">
   <si>
     <t>Шаг</t>
   </si>
@@ -238,6 +238,75 @@
       </rPr>
       <t>Пользователь на странице Авторизации по номеру телефона</t>
     </r>
+  </si>
+  <si>
+    <t>1)</t>
+  </si>
+  <si>
+    <t>Иконка сайта</t>
+  </si>
+  <si>
+    <t>2)</t>
+  </si>
+  <si>
+    <t>Кнопка "Услуги"</t>
+  </si>
+  <si>
+    <t>Кнопка "Анализы"</t>
+  </si>
+  <si>
+    <t>Кнопка "Клиники"</t>
+  </si>
+  <si>
+    <t>Кнопка "Врачи"</t>
+  </si>
+  <si>
+    <t>Кнопка "Программы"</t>
+  </si>
+  <si>
+    <t>Кнопка "Акции"</t>
+  </si>
+  <si>
+    <t>Кнопка с номером телефона</t>
+  </si>
+  <si>
+    <t>Ярлык геолокации</t>
+  </si>
+  <si>
+    <t>Кнопка "Поиск"</t>
+  </si>
+  <si>
+    <t>3)</t>
+  </si>
+  <si>
+    <t>4)</t>
+  </si>
+  <si>
+    <t>5)</t>
+  </si>
+  <si>
+    <t>6)</t>
+  </si>
+  <si>
+    <t>7)</t>
+  </si>
+  <si>
+    <t>Закрепленое "Быстрое Меню"</t>
+  </si>
+  <si>
+    <t>8)</t>
+  </si>
+  <si>
+    <t>9)</t>
+  </si>
+  <si>
+    <t>10)</t>
+  </si>
+  <si>
+    <t>11)</t>
+  </si>
+  <si>
+    <t>Пункт</t>
   </si>
 </sst>
 </file>
@@ -296,7 +365,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,6 +387,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -349,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -383,7 +458,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -766,10 +850,10 @@
       <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -783,8 +867,8 @@
       <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
     </row>
     <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A6" s="15">
@@ -796,8 +880,8 @@
       <c r="C6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
     </row>
     <row r="9" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
@@ -842,10 +926,10 @@
       <c r="C12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -859,8 +943,8 @@
       <c r="C13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
     </row>
     <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A14" s="15">
@@ -872,8 +956,8 @@
       <c r="C14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
     </row>
     <row r="17" spans="1:5" s="4" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -918,10 +1002,10 @@
       <c r="C20" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="22" t="s">
         <v>10</v>
       </c>
     </row>
@@ -935,8 +1019,8 @@
       <c r="C21" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="22"/>
     </row>
     <row r="22" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A22" s="15">
@@ -948,8 +1032,8 @@
       <c r="C22" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="22"/>
     </row>
     <row r="23" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A23" s="15">
@@ -961,8 +1045,8 @@
       <c r="C23" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="22"/>
     </row>
     <row r="24" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A24" s="15">
@@ -974,8 +1058,8 @@
       <c r="C24" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="22"/>
     </row>
     <row r="25" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A25" s="15">
@@ -987,8 +1071,8 @@
       <c r="C25" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="22"/>
     </row>
     <row r="26" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A26" s="15">
@@ -1000,8 +1084,8 @@
       <c r="C26" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="22"/>
     </row>
     <row r="27" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A27" s="15">
@@ -1013,8 +1097,8 @@
       <c r="C27" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
     </row>
     <row r="30" spans="1:5" s="4" customFormat="1" ht="19" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
@@ -1052,10 +1136,10 @@
       <c r="C32" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="21" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1069,8 +1153,8 @@
       <c r="C33" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
     </row>
     <row r="34" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A34" s="15">
@@ -1082,8 +1166,8 @@
       <c r="C34" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
     </row>
     <row r="35" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A35" s="15">
@@ -1095,8 +1179,8 @@
       <c r="C35" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D35" s="20"/>
-      <c r="E35" s="20"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
     </row>
     <row r="36" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A36" s="15">
@@ -1108,8 +1192,8 @@
       <c r="C36" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="20"/>
-      <c r="E36" s="20"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
     </row>
     <row r="40" spans="1:5" s="19" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
@@ -1147,10 +1231,10 @@
       <c r="C43" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="21" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1164,8 +1248,8 @@
       <c r="C44" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="21"/>
     </row>
     <row r="45" spans="1:5" ht="18" x14ac:dyDescent="0.2">
       <c r="A45" s="15">
@@ -1177,8 +1261,8 @@
       <c r="C45" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
     </row>
     <row r="48" spans="1:5" s="19" customFormat="1" ht="18" x14ac:dyDescent="0.2">
       <c r="A48" s="6" t="s">
@@ -1216,10 +1300,10 @@
       <c r="C51" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D51" s="20" t="s">
+      <c r="D51" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="21" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1233,23 +1317,23 @@
       <c r="C52" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="D32:D36"/>
+    <mergeCell ref="E32:E36"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="E51:E52"/>
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="E4:E6"/>
     <mergeCell ref="D12:D14"/>
     <mergeCell ref="E12:E14"/>
     <mergeCell ref="D20:D27"/>
     <mergeCell ref="E20:E27"/>
-    <mergeCell ref="D32:D36"/>
-    <mergeCell ref="E32:E36"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="E43:E45"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="E51:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -1258,9 +1342,112 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B847F22F-671E-3E48-8100-9C3FB16C0350}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A2" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A3" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A5" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A6" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A9" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A10" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A11" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A12" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="18" x14ac:dyDescent="0.2">
+      <c r="A13" s="23"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
